--- a/my_factory_app/data_imports/รายการยา.xlsx
+++ b/my_factory_app/data_imports/รายการยา.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sattarned\Documents\GitHub\Stock_PCM\my_factory_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sattarned\Documents\GitHub\PCM\my_factory_app\data_imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E949F82C-4B9D-4343-A219-DF0F11697D44}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51734B4-65E8-4218-8D2D-4BBB0991AE77}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10335" windowHeight="7485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>No.</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Band-aid ปลาสเตอร์ปิดแผล 1/100</t>
   </si>
   <si>
-    <t>ยาลดไข้ บรรเทาอาการหวัด ดีคอลเจน</t>
-  </si>
-  <si>
     <t>Anti-allergy pills/ยาแก้แพ้  1แผง/10</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>แผ่น</t>
   </si>
   <si>
-    <t>มี4เม็ด</t>
-  </si>
-  <si>
     <t>หลอด</t>
   </si>
   <si>
@@ -198,7 +192,10 @@
     <t>แพ็ค</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>ยาลดไข้ บรรเทาอาการหวัด ดีคอลเจน (1 แผงมี 4 เม็ด)</t>
+  </si>
+  <si>
+    <t>ชิ้น</t>
   </si>
 </sst>
 </file>
@@ -650,7 +647,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="29.25" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -673,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="23.25">
@@ -687,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="23.25">
@@ -701,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="23.25">
@@ -715,7 +712,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="23.25">
@@ -729,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="23.25">
@@ -743,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="23.25">
@@ -757,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="23.25">
@@ -771,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23.25">
@@ -785,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="23.25">
@@ -799,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="23.25">
@@ -813,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="23.25">
@@ -827,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="23.25">
@@ -841,7 +838,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="23.25">
@@ -855,10 +852,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="23.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="23.25">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -869,10 +866,10 @@
         <v>4</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="23.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="23.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -883,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="23.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="23.25">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -897,192 +894,189 @@
         <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="23.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="23.25">
       <c r="A20" s="3">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="23.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="23.25">
       <c r="A21" s="3">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="5">
         <v>4</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="23.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="23.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="23.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="23.25">
       <c r="A23" s="3">
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="23.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="23.25">
       <c r="A24" s="3">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="23.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="23.25">
       <c r="A25" s="3">
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="23.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="23.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="23.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="23.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="5">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="23.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="23.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="5">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="23.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="23.25">
       <c r="A29" s="3">
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="11">
         <v>1</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="23.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="23.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="5">
         <v>2</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="23.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="23.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="11">
         <v>1</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="23.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="23.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="5">
         <v>4</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="23.25">
@@ -1090,13 +1084,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="11">
         <v>1</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="23.25">
@@ -1104,13 +1098,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="5">
         <v>4</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" s="10"/>
     </row>
@@ -1119,13 +1113,13 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="9">
         <v>1</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E35" s="10"/>
     </row>
@@ -1134,13 +1128,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="5">
         <v>1</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25">
@@ -1148,13 +1142,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="11">
         <v>1</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" s="12"/>
     </row>
@@ -1163,19 +1157,17 @@
         <v>35</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="5">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="23.25">
-      <c r="A39" s="3">
-        <v>36</v>
-      </c>
+      <c r="A39" s="3"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
